--- a/stories/arbres/ATOM-SOC.PAY.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo s'assoit près de maman. Ils ouvrent une boîte de cartes. Maman dit : on nomme un pays. Hugo lit le nom : l'Espagne. Il répète : l'Espagne. Sur la carte, de l'eau bleue et du sable. Maman dit : ça, c'est un paysage. C'est la mer. Hugo dit : la mer. Autre carte : des sommets bruns. Maman dit : encore un paysage. Hugo dit : la montagne. Un pays. Un nom. Un paysage.</t>
+          <t>Hugo s'assoit près de maman. Ils ouvrent une boîte de cartes. On nomme un pays. Hugo lit le nom : l'Espagne. Il répète : l'Espagne. Sur la carte, de l'eau bleue et du sable. Ça, c'est un paysage. C'est la mer. La mer. Autre carte : des sommets bruns. Encore un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo s'assoit près de maman. Ils ouvrent une boîte de cartes.
+maman|On nomme un pays.
+narrateur|Hugo lit le nom : l'Espagne. Il répète : l'Espagne. Sur la carte, de l'eau bleue et du sable.
+maman|Ça, c'est un paysage. C'est la mer.
+enfant-m|La mer. Autre carte : des sommets bruns.
+maman|Encore un paysage.
+enfant-m|La montagne.
+narrateur|Un pays. Un nom. Un paysage.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo nomme l'Espagne. Il nomme aussi quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a dit le nom. L'Espagne. Il a dit le paysage. La mer. La montagne aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo range les cartes. Maman ferme la boîte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.PAY.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Un pays. Un nom. Un paysage.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Hugo nomme l'Espagne. Il nomme aussi quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Hugo a dit le nom. L'Espagne. Il a dit le paysage. La mer. La montagne aussi.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|Hugo range les cartes. Maman ferme la boîte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.PAY.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L'Espagne et la mer de Hugo</t>
+          <t>La carte d'Espagne de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut coller à la fenêtre la carte d'Espagne qui sent encore l'enveloppe. Le timbre se décolle. Elles le recollent. La mer bleue reste dans la lumière.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo s'assoit près de maman. Ils ouvrent une boîte de cartes. On nomme un pays. Hugo lit le nom : l'Espagne. Il répète : l'Espagne. Sur la carte, de l'eau bleue et du sable. Ça, c'est un paysage. C'est la mer. La mer. Autre carte : des sommets bruns. Encore un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
+          <t>La boîte aux lettres sent le papier chaud. Un rayon glisse sur le carrelage rouge. La cuisine sent le café un peu froid. Une enveloppe crème attend sur la table. Le bord de l'enveloppe est un peu rêche. Sarah vit ici, avec maman. Tu as vu l'enveloppe, Sarah ? Elle sent le papier. Et un peu la colle. C'est une carte d'Espagne. En ce moment, Sarah ouvre l'enveloppe. Le papier fait un petit bruit sec. Une carte postale glisse dans sa main. Le recto est tout bleu. De l'eau ! Beaucoup d'eau bleue. Oui. C'est la mer d'Espagne. L'Espagne. Et la mer. Sarah approche la carte de son nez. Ça sent encore l'enveloppe. Un peu de sel, presque. Tu veux la mettre où ? À la fenêtre. Pour voir la mer. Un petit bateau blanc est dessiné. Sarah le suit du doigt. Le doigt laisse une trace chaude. Tu le sens, le papier ? Il est un peu rêche. Le timbre est orange, un peu gondolé. Sarah veut coller la carte. Elle tient le timbre du pouce. Le timbre se décolle, tout seul. Oh. Il part ! Doucement. On le recolle ensemble ? Oui, maman. Le timbre tremble entre deux doigts. Un coin blanc montre la colle sèche. Sarah souffle dessus, tout bas. Il ne tient plus. Le bâton de colle est dans le tiroir. Sarah tire le tiroir. Les cuillères tintent un peu. Le bâton est bleu, un peu dur. Je le tourne ? Oui, tout doucement.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo s'assoit près de maman. Ils ouvrent une boîte de cartes. Maman dit : on &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me un pays. Hugo lit le nom : l'Espagne. Il répète : l'Espagne. Sur la carte, de l'eau bleue et du sable. Maman dit : ça, c'est un paysage. C'est la mer. Hugo dit : la mer. Autre carte : des sommets bruns. Maman dit : encore un paysage. Hugo dit : la montagne. Un pays. Un nom. Un paysage.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La boîte aux lettres sent le papier chaud. Un rayon glisse sur le carrelage rouge. La cuisine sent le café un peu froid. Une enveloppe crème attend sur la table. Le bord de l'enveloppe est un peu rêche. Sarah vit ici, avec maman. Tu as vu l'enveloppe, Sarah ? Elle sent le papier. Et un peu la colle. C'est une carte d'Espagne. En ce moment, Sarah ouvre l'enveloppe. Le papier fait un petit bruit sec. Une carte postale glisse dans sa main. Le recto est tout bleu. De l'eau ! Beaucoup d'eau bleue. Oui. C'est la mer d'Espagne. L'Espagne. Et la mer. Sarah approche la carte de son nez. Ça sent encore l'enveloppe. Un peu de sel, presque. Tu veux la mettre où ? À la fenêtre. Pour voir la mer. Un petit bateau blanc est dessiné. Sarah le suit du doigt. Le doigt laisse une trace chaude. Tu le sens, le papier ? Il est un peu rêche. Le timbre est orange, un peu gondolé. Sarah veut coller la carte. Elle tient le timbre du pouce. Le timbre se décolle, tout seul. Oh. Il part ! Doucement. On le recolle ensemble ? Oui, maman. Le timbre tremble entre deux doigts. Un coin blanc montre la colle sèche. Sarah souffle dessus, tout bas. Il ne tient plus. Le bâton de colle est dans le tiroir. Sarah tire le tiroir. Les cuillères tintent un peu. Le bâton est bleu, un peu dur. Je le tourne ? Oui, tout doucement.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,17 +1324,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugo s'assoit près de maman. Ils ouvrent une boîte de cartes.
-maman|On nomme un pays.
-narrateur|Hugo lit le nom : l'Espagne. Il répète : l'Espagne. Sur la carte, de l'eau bleue et du sable.
-maman|Ça, c'est un paysage. C'est la mer.
-enfant-m|La mer. Autre carte : des sommets bruns.
-maman|Encore un paysage.
-enfant-m|La montagne.
-narrateur|Un pays. Un nom. Un paysage.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La boîte aux lettres sent le papier chaud.
+narrateur|Un rayon glisse sur le carrelage rouge.
+narrateur|La cuisine sent le café un peu froid.
+narrateur|Une enveloppe crème attend sur la table.
+narrateur|Le bord de l'enveloppe est un peu rêche.
+narrateur|Sarah vit ici, avec maman.
+maman|Tu as vu l'enveloppe, Sarah ?
+enfant-f|Elle sent le papier.
+enfant-f|Et un peu la colle.
+maman|C'est une carte d'Espagne.
+narrateur|En ce moment, Sarah ouvre l'enveloppe.
+narrateur|Le papier fait un petit bruit sec.
+narrateur|Une carte postale glisse dans sa main.
+narrateur|Le recto est tout bleu.
+enfant-f|De l'eau !
+enfant-f|Beaucoup d'eau bleue.
+maman|Oui.
+maman|C'est la mer d'Espagne.
+enfant-f|L'Espagne.
+enfant-f|Et la mer.
+narrateur|Sarah approche la carte de son nez.
+narrateur|Ça sent encore l'enveloppe.
+narrateur|Un peu de sel, presque.
+maman|Tu veux la mettre où ?
+enfant-f|À la fenêtre.
+enfant-f|Pour voir la mer.
+narrateur|Un petit bateau blanc est dessiné.
+narrateur|Sarah le suit du doigt.
+narrateur|Le doigt laisse une trace chaude.
+maman|Tu le sens, le papier ?
+enfant-f|Il est un peu rêche.
+narrateur|Le timbre est orange, un peu gondolé.
+narrateur|Sarah veut coller la carte.
+narrateur|Elle tient le timbre du pouce.
+narrateur|Le timbre se décolle, tout seul.
+enfant-f|Oh.
+enfant-f|Il part !
+maman|Doucement.
+maman|On le recolle ensemble ?
+enfant-f|Oui, maman.
+narrateur|Le timbre tremble entre deux doigts.
+narrateur|Un coin blanc montre la colle sèche.
+narrateur|Sarah souffle dessus, tout bas.
+enfant-f|Il ne tient plus.
+maman|Le bâton de colle est dans le tiroir.
+narrateur|Sarah tire le tiroir.
+narrateur|Les cuillères tintent un peu.
+narrateur|Le bâton est bleu, un peu dur.
+enfant-f|Je le tourne ?
+maman|Oui, tout doucement.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,12 +1400,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hugo nomme l'Espagne. Il nomme aussi quoi ?</t>
+          <t>Sarah tient la carte d'Espagne. Elle nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me l'Espagne. Il nomme aussi quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah tient la carte d'Espagne. Elle nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1367,7 +1420,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la mer | un paysage | un pays | l'Espagne</t>
+          <t>mer | la mer | mer d'Espagne | l'eau | eau bleue</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1382,7 +1435,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il y a de l'eau bleue. C'est quel paysage ?</t>
+          <t>La carte montre la mer. Sarah nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1424,14 +1477,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1507,10 +1560,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hugo nomme l'Espagne. Il nomme aussi quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah tient la carte d'Espagne.
+narrateur|Elle nomme aussi quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,12 +1588,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo a dit le nom. L'Espagne. Il a dit le paysage. La mer. La montagne aussi.</t>
+          <t>Sarah tourne le bâton de colle. Une petite lune blanche apparaît. Un peu, pas trop. Sarah pose la colle sur le timbre. Le papier devient un peu luisant. C'est froid. Oui. Maintenant on presse. Sarah pose le timbre orange. Elle appuie avec le pouce. Le pouce reste une seconde. Il tient ? Il tient. Merci, Sarah. La carte sent encore l'enveloppe. Et un peu la colle neuve. L'Espagne. La mer. Un pays. Un paysage. Elles marchent vers la fenêtre. Le carreau est tiède sous la main.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;. L'Espagne. Il a dit le paysage. La mer. La montagne aussi.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah tourne le bâton de colle. Une petite lune blanche apparaît. Un peu, pas trop. Sarah pose la colle sur le timbre. Le papier devient un peu luisant. C'est froid. Oui. Maintenant on presse. Sarah pose le timbre orange. Elle appuie avec le pouce. Le pouce reste une seconde. Il tient ? Il tient. Merci, Sarah. La carte sent encore l'enveloppe. Et un peu la colle neuve. L'Espagne. La mer. Un pays. Un paysage. Elles marchent vers la fenêtre. Le carreau est tiède sous la main.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1603,7 +1656,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1679,10 +1732,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a dit le nom. L'Espagne. Il a dit le paysage. La mer. La montagne aussi.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah tourne le bâton de colle.
+narrateur|Une petite lune blanche apparaît.
+maman|Un peu, pas trop.
+narrateur|Sarah pose la colle sur le timbre.
+narrateur|Le papier devient un peu luisant.
+enfant-f|C'est froid.
+maman|Oui.
+maman|Maintenant on presse.
+narrateur|Sarah pose le timbre orange.
+narrateur|Elle appuie avec le pouce.
+narrateur|Le pouce reste une seconde.
+maman|Il tient ?
+enfant-f|Il tient.
+maman|Merci, Sarah.
+narrateur|La carte sent encore l'enveloppe.
+narrateur|Et un peu la colle neuve.
+enfant-f|L'Espagne.
+enfant-f|La mer.
+maman|Un pays.
+maman|Un paysage.
+narrateur|Elles marchent vers la fenêtre.
+narrateur|Le carreau est tiède sous la main.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1707,12 +1780,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hugo range les cartes. Maman ferme la boîte.</t>
+          <t>Sarah pose la carte contre le verre. Tu la tiens. Je mets le scotch. Un petit bruit de papier collant. La mer bleue se tient toute seule. Elle reste ! Oui. Tu la verras demain matin. Le timbre orange est bien plat. Sarah le caresse du bout du doigt. Il ne part plus. Vous avez recollé ensemble. Tu as fini de presser ? Oui, maman. Un nuage passe sur le bleu. Puis le soleil revient.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo range les cartes. Maman ferme la boîte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah pose la carte contre le verre. Tu la tiens. Je mets le scotch. Un petit bruit de papier collant. La mer bleue se tient toute seule. Elle reste ! Oui. Tu la verras demain matin. Le timbre orange est bien plat. Sarah le caresse du bout du doigt. Il ne part plus. Vous avez recollé ensemble. Tu as fini de presser ? Oui, maman. Un nuage passe sur le bleu. Puis le soleil revient.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1775,7 +1848,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1843,10 +1916,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hugo range les cartes. Maman ferme la boîte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah pose la carte contre le verre.
+maman|Tu la tiens.
+maman|Je mets le scotch.
+narrateur|Un petit bruit de papier collant.
+narrateur|La mer bleue se tient toute seule.
+enfant-f|Elle reste !
+maman|Oui.
+maman|Tu la verras demain matin.
+narrateur|Le timbre orange est bien plat.
+narrateur|Sarah le caresse du bout du doigt.
+enfant-f|Il ne part plus.
+maman|Vous avez recollé ensemble.
+maman|Tu as fini de presser ?
+enfant-f|Oui, maman.
+narrateur|Un nuage passe sur le bleu.
+narrateur|Puis le soleil revient.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1871,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La carte d'Espagne reste à la fenêtre. Ça sent encore l'enveloppe, tout près. La mer est là. L'Espagne aussi. Le timbre orange tient dans la lumière.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La carte d'Espagne reste à la fenêtre. Ça sent encore l'enveloppe, tout près. La mer est là. L'Espagne aussi. Le timbre orange tient dans la lumière.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1939,7 +2026,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2011,10 +2098,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La carte d'Espagne reste à la fenêtre.
+narrateur|Ça sent encore l'enveloppe, tout près.
+enfant-f|La mer est là.
+maman|L'Espagne aussi.
+narrateur|Le timbre orange tient dans la lumière.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.PAY.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>cuisine puis fenêtre, après le courrier</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hugo, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>
